--- a/output/trinidad_gas.xlsx
+++ b/output/trinidad_gas.xlsx
@@ -18,7 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -57,9 +60,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,9 +535,977 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>mmscfd</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BPTT</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1026.336788387097</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BPTT</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>979.2966325</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BPTT</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>951.4172364516129</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BPTT</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>950.9620363333333</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BPTT</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>948.2965261290323</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>HPCL (Offshore)</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>16.4531561949079</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HPCL (Offshore)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>16.20455218451762</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HPCL (Offshore)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HPCL (Offshore)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HPCL (Offshore)</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HPCL (Land)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.18758064516129</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HPCL (Land)</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HPCL (Land)</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HPCL (Land)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HPCL (Land)</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>444.484409916129</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>462.4207461452858</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>433.4296774193548</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>557.9616666666667</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>553.5893548387098</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>451.033129032258</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>493.13425</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>468.7631935483871</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>435.6668</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>407.8799677419355</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PERENCO</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>457.1356638387097</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PERENCO</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>462.7298139286787</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PERENCO</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>453.9978283873871</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PERENCO</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>450.0629813334</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PERENCO</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>462.5357477417097</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PROMAN</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>16.3683870967742</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PROMAN</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>22.03821428571428</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PROMAN</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>15.72967741935484</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PROMAN</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>24.957</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PROMAN</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>21.85129032258065</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TOUCHSTONE</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>33.13036737158834</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>TOUCHSTONE</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>32.02750874533133</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TOUCHSTONE</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>28.85115734084676</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>TOUCHSTONE</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>31.25039027115517</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>TOUCHSTONE</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>29.2279456405902</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2446.129482482625</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2469.851717789528</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2368.188770566943</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2466.860874604555</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2439.380832414558</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -544,9 +1516,1187 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>mmscfd</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Power Generation</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>228.6094279032258</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Power Generation</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>238.1228512142857</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Power Generation</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>262.3959126451613</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Power Generation</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>261.0417272</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Power Generation</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>280.9516371290322</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ammonia Manufacture</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>338.8833337741936</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ammonia Manufacture</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>351.51826125</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ammonia Manufacture</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>337.9258685483871</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ammonia Manufacture</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>334.4178742666667</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ammonia Manufacture</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>324.0366067419355</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Methanol Manufacture</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>362.9577847741936</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Methanol Manufacture</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>488.8524171071429</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Methanol Manufacture</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>494.8642808709678</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Methanol Manufacture</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>360.6807472666667</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Methanol Manufacture</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>389.3707865806451</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Iron &amp; Steel Manufacture</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>48.34645141935484</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Iron &amp; Steel Manufacture</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>48.48315382142857</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Iron &amp; Steel Manufacture</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>49.04823716129032</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Iron &amp; Steel Manufacture</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>49.3296688</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Iron &amp; Steel Manufacture</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>50.86026519354839</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Cement Manufacture</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.99594383870968</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Cement Manufacture</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10.44181525</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Cement Manufacture</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10.80526448387097</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Cement Manufacture</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.84396126666667</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cement Manufacture</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>9.712596193548388</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ammonia Derivatives</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>8.277382967741936</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ammonia Derivatives</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>6.407504964285714</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ammonia Derivatives</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>6.20377635483871</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ammonia Derivatives</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>5.9617682</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ammonia Derivatives</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>6.805560774193548</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Gas Processing</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>16.34390193548387</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Gas Processing</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>17.87620646428572</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Gas Processing</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>17.22915322580645</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Gas Processing</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>17.2291516</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Gas Processing</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>14.89712290322581</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Small Consumers</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>8</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Small Consumers</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.31081414285714</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Small Consumers</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>8.174505483870968</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Small Consumers</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.39455563333333</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Small Consumers</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>NGC 4" Sales to bpTT</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.9179354838709678</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>NGC 4" Sales to bpTT</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.6729285714285714</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NGC 4" Sales to bpTT</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1.052129032258065</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>NGC 4" Sales to bpTT</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1.052129032258065</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>NGC 4" Sales to bpTT</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1.026733333333333</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>LNG</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1241.646029354839</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>LNG</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1144.444786321429</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>LNG</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1032.746351612903</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>LNG</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1255.312466666667</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>LNG</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1170.524580967742</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2265.978191451613</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2317.130739107143</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2220.445479419355</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2307.264049932258</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2260.185889817204</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/trinidad_gas.xlsx
+++ b/output/trinidad_gas.xlsx
@@ -486,7 +486,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Monthly from January 2021. Each year comes from that year's bulletin workbook (full-year editions for past years, amended Nov 2025; the current year-to-date edition for this year), found on every run from the ministry's bulletin category pages, so a newly posted year is picked up automatically. Where two editions cover the same month the most recently published one wins; the 'source' column names the workbook used. Months not yet reached in a year-to-date edition show as 0 in the source and are dropped rather than kept as fake zero readings. 2025 has no full-year edition posted yet (as of Oct 2026), so it is a gap until MEEI publishes one.</t>
+          <t>Monthly from January 2021. Each year comes from that year's bulletin workbook (full-year editions for past years, amended Nov 2025; the current year-to-date edition for this year), found on every run from the ministry's bulletin category pages, so a newly posted year is picked up automatically. Where two editions cover the same month the most recently published one wins; the 'source' column names the workbook used. Months not yet reached in a year-to-date edition show as 0 in the source and are dropped rather than kept as fake zero readings. Bulletin posts are found from both the category pages and the site's post sitemap (the Jan-Dec 2025 edition is only in the latter). Runs are incremental: years already complete in this archive are not downloaded again; each run reads the current year-to-date bulletin plus any year with missing months. Use --full to rebuild from scratch.</t>
         </is>
       </c>
     </row>

--- a/output/trinidad_gas.xlsx
+++ b/output/trinidad_gas.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F505"/>
+  <dimension ref="A1:F619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12504,7 +12504,7 @@
         <v>459</v>
       </c>
       <c r="B461" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         </is>
       </c>
       <c r="D461" t="n">
-        <v>1026.336788387097</v>
+        <v>1039.08014451612</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -12530,15 +12530,15 @@
         <v>460</v>
       </c>
       <c r="B462" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>DENOVO</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>444.484409916129</v>
+        <v>28.8190322580645</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -12556,15 +12556,15 @@
         <v>461</v>
       </c>
       <c r="B463" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>HPCL (Land)</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>1.18758064516129</v>
+        <v>416.6660061290323</v>
       </c>
       <c r="E463" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -12582,15 +12582,15 @@
         <v>462</v>
       </c>
       <c r="B464" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>HPCL (Offshore)</t>
+          <t>HPCL (Land)</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>16.4531561949079</v>
+        <v>1.588290322580645</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -12608,15 +12608,15 @@
         <v>463</v>
       </c>
       <c r="B465" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>PERENCO</t>
+          <t>HPCL (Offshore)</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>457.1356638387097</v>
+        <v>16.79081839096703</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -12634,15 +12634,15 @@
         <v>464</v>
       </c>
       <c r="B466" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>PROMAN</t>
+          <t>PERENCO</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>16.3683870967742</v>
+        <v>213.093083870967</v>
       </c>
       <c r="E466" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -12660,7 +12660,7 @@
         <v>465</v>
       </c>
       <c r="B467" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C467" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         </is>
       </c>
       <c r="D467" t="n">
-        <v>451.033129032258</v>
+        <v>561.628064516129</v>
       </c>
       <c r="E467" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -12686,7 +12686,7 @@
         <v>466</v>
       </c>
       <c r="B468" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C468" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="D468" t="n">
-        <v>2446.129482482625</v>
+        <v>2622.328465810312</v>
       </c>
       <c r="E468" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -12712,7 +12712,7 @@
         <v>467</v>
       </c>
       <c r="B469" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C469" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         </is>
       </c>
       <c r="D469" t="n">
-        <v>33.13036737158834</v>
+        <v>26.6879193548387</v>
       </c>
       <c r="E469" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -12738,15 +12738,15 @@
         <v>468</v>
       </c>
       <c r="B470" s="2" t="n">
-        <v>46054</v>
+        <v>45658</v>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>BPTT</t>
+          <t>WOODSIDE</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>979.2966325</v>
+        <v>317.975106451612</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -12764,15 +12764,15 @@
         <v>469</v>
       </c>
       <c r="B471" s="2" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>BPTT</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>462.4207461452858</v>
+        <v>929.618384642857</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -12790,15 +12790,15 @@
         <v>470</v>
       </c>
       <c r="B472" s="2" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>HPCL (Land)</t>
+          <t>DENOVO</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>2</v>
+        <v>28.5771428571428</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -12816,15 +12816,15 @@
         <v>471</v>
       </c>
       <c r="B473" s="2" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>HPCL (Offshore)</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>16.20455218451762</v>
+        <v>412.97739125</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -12842,15 +12842,15 @@
         <v>472</v>
       </c>
       <c r="B474" s="2" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>PERENCO</t>
+          <t>HPCL (Land)</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>462.7298139286787</v>
+        <v>1.636678571428571</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -12868,15 +12868,15 @@
         <v>473</v>
       </c>
       <c r="B475" s="2" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>PROMAN</t>
+          <t>HPCL (Offshore)</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>22.03821428571428</v>
+        <v>22.7549437929543</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -12894,15 +12894,15 @@
         <v>474</v>
       </c>
       <c r="B476" s="2" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>PERENCO</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>493.13425</v>
+        <v>217.798763928571</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -12920,15 +12920,15 @@
         <v>475</v>
       </c>
       <c r="B477" s="2" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>2469.851717789528</v>
+        <v>552.838392857142</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -12946,15 +12946,15 @@
         <v>476</v>
       </c>
       <c r="B478" s="2" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>TOUCHSTONE</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>32.02750874533133</v>
+        <v>2500.429060042953</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -12972,15 +12972,15 @@
         <v>477</v>
       </c>
       <c r="B479" s="2" t="n">
-        <v>46082</v>
+        <v>45689</v>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>BPTT</t>
+          <t>TOUCHSTONE</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>951.4172364516129</v>
+        <v>23.1361003571428</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -12998,15 +12998,15 @@
         <v>478</v>
       </c>
       <c r="B480" s="2" t="n">
-        <v>46082</v>
+        <v>45689</v>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>WOODSIDE</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>433.4296774193548</v>
+        <v>311.091261785714</v>
       </c>
       <c r="E480" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13024,15 +13024,15 @@
         <v>479</v>
       </c>
       <c r="B481" s="2" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>HPCL (Land)</t>
+          <t>BPTT</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>2</v>
+        <v>845.731029032258</v>
       </c>
       <c r="E481" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13050,15 +13050,15 @@
         <v>480</v>
       </c>
       <c r="B482" s="2" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>HPCL (Offshore)</t>
+          <t>DENOVO</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>14</v>
+        <v>29.0890322580645</v>
       </c>
       <c r="E482" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13076,15 +13076,15 @@
         <v>481</v>
       </c>
       <c r="B483" s="2" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>PERENCO</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>453.9978283873871</v>
+        <v>388.5336739812838</v>
       </c>
       <c r="E483" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13102,15 +13102,15 @@
         <v>482</v>
       </c>
       <c r="B484" s="2" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>PROMAN</t>
+          <t>HPCL (Land)</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>15.72967741935484</v>
+        <v>1.521129032258065</v>
       </c>
       <c r="E484" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13128,15 +13128,15 @@
         <v>483</v>
       </c>
       <c r="B485" s="2" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>HPCL (Offshore)</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>468.7631935483871</v>
+        <v>23.40172621000641</v>
       </c>
       <c r="E485" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13154,15 +13154,15 @@
         <v>484</v>
       </c>
       <c r="B486" s="2" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>PERENCO</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>2368.188770566943</v>
+        <v>215.2814129032285</v>
       </c>
       <c r="E486" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13180,15 +13180,15 @@
         <v>485</v>
       </c>
       <c r="B487" s="2" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>TOUCHSTONE</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>28.85115734084676</v>
+        <v>527.6630709677419</v>
       </c>
       <c r="E487" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13206,15 +13206,15 @@
         <v>486</v>
       </c>
       <c r="B488" s="2" t="n">
-        <v>46113</v>
+        <v>45717</v>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>BPTT</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>950.9620363333333</v>
+        <v>2357.564906642905</v>
       </c>
       <c r="E488" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13232,15 +13232,15 @@
         <v>487</v>
       </c>
       <c r="B489" s="2" t="n">
-        <v>46113</v>
+        <v>45717</v>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>TOUCHSTONE</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>557.9616666666667</v>
+        <v>20.3489632258064</v>
       </c>
       <c r="E489" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13258,15 +13258,15 @@
         <v>488</v>
       </c>
       <c r="B490" s="2" t="n">
-        <v>46113</v>
+        <v>45717</v>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>HPCL (Land)</t>
+          <t>WOODSIDE</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>2</v>
+        <v>305.994869032258</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13284,15 +13284,15 @@
         <v>489</v>
       </c>
       <c r="B491" s="2" t="n">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>HPCL (Offshore)</t>
+          <t>BPTT</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>14</v>
+        <v>957.6102658170601</v>
       </c>
       <c r="E491" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13310,15 +13310,15 @@
         <v>490</v>
       </c>
       <c r="B492" s="2" t="n">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>PERENCO</t>
+          <t>DENOVO</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>450.0629813334</v>
+        <v>25.93608909992053</v>
       </c>
       <c r="E492" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13336,15 +13336,15 @@
         <v>491</v>
       </c>
       <c r="B493" s="2" t="n">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>PROMAN</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>24.957</v>
+        <v>391.5005833749467</v>
       </c>
       <c r="E493" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13362,15 +13362,15 @@
         <v>492</v>
       </c>
       <c r="B494" s="2" t="n">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>HPCL (Land)</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>435.6668</v>
+        <v>1.5082</v>
       </c>
       <c r="E494" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13388,15 +13388,15 @@
         <v>493</v>
       </c>
       <c r="B495" s="2" t="n">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>HPCL (Offshore)</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>2466.860874604555</v>
+        <v>23.39061542783074</v>
       </c>
       <c r="E495" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13414,15 +13414,15 @@
         <v>494</v>
       </c>
       <c r="B496" s="2" t="n">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>TOUCHSTONE</t>
+          <t>PERENCO</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>31.25039027115517</v>
+        <v>179.4892976666665</v>
       </c>
       <c r="E496" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13440,15 +13440,15 @@
         <v>495</v>
       </c>
       <c r="B497" s="2" t="n">
-        <v>46143</v>
+        <v>45748</v>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>BPTT</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>948.2965261290323</v>
+        <v>512.5378633333333</v>
       </c>
       <c r="E497" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13466,15 +13466,15 @@
         <v>496</v>
       </c>
       <c r="B498" s="2" t="n">
-        <v>46143</v>
+        <v>45748</v>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>553.5893548387098</v>
+        <v>2423.130496386425</v>
       </c>
       <c r="E498" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13492,15 +13492,15 @@
         <v>497</v>
       </c>
       <c r="B499" s="2" t="n">
-        <v>46143</v>
+        <v>45748</v>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>HPCL (Land)</t>
+          <t>TOUCHSTONE</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>2</v>
+        <v>18.35788333333333</v>
       </c>
       <c r="E499" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13518,15 +13518,15 @@
         <v>498</v>
       </c>
       <c r="B500" s="2" t="n">
-        <v>46143</v>
+        <v>45748</v>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>HPCL (Offshore)</t>
+          <t>WOODSIDE</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>14</v>
+        <v>312.7996983333333</v>
       </c>
       <c r="E500" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13544,15 +13544,15 @@
         <v>499</v>
       </c>
       <c r="B501" s="2" t="n">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>PERENCO</t>
+          <t>BPTT</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>462.5357477417097</v>
+        <v>1191.23793390657</v>
       </c>
       <c r="E501" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13570,15 +13570,15 @@
         <v>500</v>
       </c>
       <c r="B502" s="2" t="n">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>PROMAN</t>
+          <t>DENOVO</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>21.85129032258065</v>
+        <v>28.8787096774194</v>
       </c>
       <c r="E502" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13596,15 +13596,15 @@
         <v>501</v>
       </c>
       <c r="B503" s="2" t="n">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>407.8799677419355</v>
+        <v>412.731764193548</v>
       </c>
       <c r="E503" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13622,15 +13622,15 @@
         <v>502</v>
       </c>
       <c r="B504" s="2" t="n">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>HPCL (Land)</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>2439.380832414558</v>
+        <v>1.518096774193548</v>
       </c>
       <c r="E504" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -13648,22 +13648,2986 @@
         <v>503</v>
       </c>
       <c r="B505" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>HPCL (Offshore)</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>19.03460262869815</v>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>504</v>
+      </c>
+      <c r="B506" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>PERENCO</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>218.594135161297</v>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>505</v>
+      </c>
+      <c r="B507" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>542.685129032258</v>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>506</v>
+      </c>
+      <c r="B508" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>2734.033206553619</v>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>507</v>
+      </c>
+      <c r="B509" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>TOUCHSTONE</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>26.47835117963555</v>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>508</v>
+      </c>
+      <c r="B510" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>WOODSIDE</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>292.874484</v>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>509</v>
+      </c>
+      <c r="B511" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>BPTT</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>1101.613848937423</v>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>510</v>
+      </c>
+      <c r="B512" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>DENOVO</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>27.20766666666667</v>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>511</v>
+      </c>
+      <c r="B513" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>474.9391851058127</v>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>512</v>
+      </c>
+      <c r="B514" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>HPCL (Land)</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>1.432833333333333</v>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>513</v>
+      </c>
+      <c r="B515" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>HPCL (Offshore)</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>20.21343587121467</v>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>514</v>
+      </c>
+      <c r="B516" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>PERENCO</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>221.0326666666667</v>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>515</v>
+      </c>
+      <c r="B517" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>492.9115</v>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>516</v>
+      </c>
+      <c r="B518" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>2668.07545135834</v>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>517</v>
+      </c>
+      <c r="B519" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>TOUCHSTONE</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>33.09276611055687</v>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>518</v>
+      </c>
+      <c r="B520" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>WOODSIDE</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>295.6315486666666</v>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>519</v>
+      </c>
+      <c r="B521" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>BPTT</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>1139.225344960971</v>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>520</v>
+      </c>
+      <c r="B522" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>DENOVO</t>
+        </is>
+      </c>
+      <c r="D522" t="n">
+        <v>28.4958064516129</v>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>521</v>
+      </c>
+      <c r="B523" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D523" t="n">
+        <v>442.5</v>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>522</v>
+      </c>
+      <c r="B524" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>HPCL (Land)</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>1.330935483870968</v>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>523</v>
+      </c>
+      <c r="B525" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>HPCL (Offshore)</t>
+        </is>
+      </c>
+      <c r="D525" t="n">
+        <v>19.95228675968863</v>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>524</v>
+      </c>
+      <c r="B526" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>PERENCO</t>
+        </is>
+      </c>
+      <c r="D526" t="n">
+        <v>545.0465748709678</v>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>525</v>
+      </c>
+      <c r="B527" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="D527" t="n">
+        <v>472.8811290322581</v>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>526</v>
+      </c>
+      <c r="B528" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D528" t="n">
+        <v>2683.776674527111</v>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>527</v>
+      </c>
+      <c r="B529" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>TOUCHSTONE</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>34.34459696774194</v>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>528</v>
+      </c>
+      <c r="B530" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>BPTT</t>
+        </is>
+      </c>
+      <c r="D530" t="n">
+        <v>1049.384453483381</v>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>529</v>
+      </c>
+      <c r="B531" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>DENOVO</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>29.54064516129032</v>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>530</v>
+      </c>
+      <c r="B532" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D532" t="n">
+        <v>460.1063618117742</v>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>531</v>
+      </c>
+      <c r="B533" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>HPCL (Land)</t>
+        </is>
+      </c>
+      <c r="D533" t="n">
+        <v>1.371193548387097</v>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>532</v>
+      </c>
+      <c r="B534" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>HPCL (Offshore)</t>
+        </is>
+      </c>
+      <c r="D534" t="n">
+        <v>20.59830887408857</v>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>533</v>
+      </c>
+      <c r="B535" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>PERENCO</t>
+        </is>
+      </c>
+      <c r="D535" t="n">
+        <v>536.4744193548387</v>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>534</v>
+      </c>
+      <c r="B536" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="D536" t="n">
+        <v>521.2793548387097</v>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>535</v>
+      </c>
+      <c r="B537" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D537" t="n">
+        <v>2653.891114446166</v>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>536</v>
+      </c>
+      <c r="B538" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>TOUCHSTONE</t>
+        </is>
+      </c>
+      <c r="D538" t="n">
+        <v>35.1363773736967</v>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>537</v>
+      </c>
+      <c r="B539" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>BPTT</t>
+        </is>
+      </c>
+      <c r="D539" t="n">
+        <v>1004.044444974734</v>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>538</v>
+      </c>
+      <c r="B540" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>DENOVO</t>
+        </is>
+      </c>
+      <c r="D540" t="n">
+        <v>29.43233333333334</v>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>539</v>
+      </c>
+      <c r="B541" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D541" t="n">
+        <v>504.8747490341233</v>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>540</v>
+      </c>
+      <c r="B542" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>HPCL (Land)</t>
+        </is>
+      </c>
+      <c r="D542" t="n">
+        <v>1.272066666666667</v>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>541</v>
+      </c>
+      <c r="B543" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>HPCL (Offshore)</t>
+        </is>
+      </c>
+      <c r="D543" t="n">
+        <v>18.71038081875562</v>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>542</v>
+      </c>
+      <c r="B544" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>PERENCO</t>
+        </is>
+      </c>
+      <c r="D544" t="n">
+        <v>479.3268999999999</v>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>543</v>
+      </c>
+      <c r="B545" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="D545" t="n">
+        <v>433.0575666666667</v>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>544</v>
+      </c>
+      <c r="B546" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D546" t="n">
+        <v>2503.500633063591</v>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>545</v>
+      </c>
+      <c r="B547" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>TOUCHSTONE</t>
+        </is>
+      </c>
+      <c r="D547" t="n">
+        <v>32.78219156931159</v>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>546</v>
+      </c>
+      <c r="B548" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>BPTT</t>
+        </is>
+      </c>
+      <c r="D548" t="n">
+        <v>986.7818267741935</v>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>547</v>
+      </c>
+      <c r="B549" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>DENOVO</t>
+        </is>
+      </c>
+      <c r="D549" t="n">
+        <v>28.02677419354839</v>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>548</v>
+      </c>
+      <c r="B550" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D550" t="n">
+        <v>432.4514916769516</v>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>549</v>
+      </c>
+      <c r="B551" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>HPCL (Land)</t>
+        </is>
+      </c>
+      <c r="D551" t="n">
+        <v>1.207032258064516</v>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>550</v>
+      </c>
+      <c r="B552" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>HPCL (Offshore)</t>
+        </is>
+      </c>
+      <c r="D552" t="n">
+        <v>18.04875563105382</v>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>551</v>
+      </c>
+      <c r="B553" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>PERENCO</t>
+        </is>
+      </c>
+      <c r="D553" t="n">
+        <v>465.4581225806451</v>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>552</v>
+      </c>
+      <c r="B554" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="D554" t="n">
+        <v>468.9247741935484</v>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>553</v>
+      </c>
+      <c r="B555" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D555" t="n">
+        <v>2432.044686389769</v>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>554</v>
+      </c>
+      <c r="B556" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>TOUCHSTONE</t>
+        </is>
+      </c>
+      <c r="D556" t="n">
+        <v>31.14590908176334</v>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>555</v>
+      </c>
+      <c r="B557" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>BPTT</t>
+        </is>
+      </c>
+      <c r="D557" t="n">
+        <v>1008.745607</v>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>556</v>
+      </c>
+      <c r="B558" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>DENOVO</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>22.81466666666667</v>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>557</v>
+      </c>
+      <c r="B559" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D559" t="n">
+        <v>409.884876356</v>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>558</v>
+      </c>
+      <c r="B560" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>HPCL (Land)</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>1.269666666666667</v>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>559</v>
+      </c>
+      <c r="B561" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>HPCL (Offshore)</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>18.58308000293153</v>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>560</v>
+      </c>
+      <c r="B562" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>PERENCO</t>
+        </is>
+      </c>
+      <c r="D562" t="n">
+        <v>480.8894073333333</v>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>561</v>
+      </c>
+      <c r="B563" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="D563" t="n">
+        <v>470.6341333333334</v>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>562</v>
+      </c>
+      <c r="B564" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D564" t="n">
+        <v>2443.798758583348</v>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>563</v>
+      </c>
+      <c r="B565" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>TOUCHSTONE</t>
+        </is>
+      </c>
+      <c r="D565" t="n">
+        <v>30.97732122441633</v>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>564</v>
+      </c>
+      <c r="B566" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>BPTT</t>
+        </is>
+      </c>
+      <c r="D566" t="n">
+        <v>1028.38586</v>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>565</v>
+      </c>
+      <c r="B567" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>DENOVO</t>
+        </is>
+      </c>
+      <c r="D567" t="n">
+        <v>27.69903225806451</v>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>566</v>
+      </c>
+      <c r="B568" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D568" t="n">
+        <v>405.7867045474648</v>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>567</v>
+      </c>
+      <c r="B569" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>HPCL (Land)</t>
+        </is>
+      </c>
+      <c r="D569" t="n">
+        <v>1.681387096774194</v>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>568</v>
+      </c>
+      <c r="B570" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>HPCL (Offshore)</t>
+        </is>
+      </c>
+      <c r="D570" t="n">
+        <v>16.72717533457348</v>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>569</v>
+      </c>
+      <c r="B571" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>PERENCO</t>
+        </is>
+      </c>
+      <c r="D571" t="n">
+        <v>476.7183971935484</v>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>570</v>
+      </c>
+      <c r="B572" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="D572" t="n">
+        <v>479.2349677419355</v>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>571</v>
+      </c>
+      <c r="B573" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D573" t="n">
+        <v>2470.866797075586</v>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>572</v>
+      </c>
+      <c r="B574" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>TOUCHSTONE</t>
+        </is>
+      </c>
+      <c r="D574" t="n">
+        <v>34.63327290322581</v>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>573</v>
+      </c>
+      <c r="B575" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>BPTT</t>
+        </is>
+      </c>
+      <c r="D575" t="n">
+        <v>1026.336788387097</v>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>574</v>
+      </c>
+      <c r="B576" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D576" t="n">
+        <v>444.484409916129</v>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>575</v>
+      </c>
+      <c r="B577" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>HPCL (Land)</t>
+        </is>
+      </c>
+      <c r="D577" t="n">
+        <v>1.18758064516129</v>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>576</v>
+      </c>
+      <c r="B578" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>HPCL (Offshore)</t>
+        </is>
+      </c>
+      <c r="D578" t="n">
+        <v>16.4531561949079</v>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>577</v>
+      </c>
+      <c r="B579" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>PERENCO</t>
+        </is>
+      </c>
+      <c r="D579" t="n">
+        <v>457.1356638387097</v>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>578</v>
+      </c>
+      <c r="B580" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>PROMAN</t>
+        </is>
+      </c>
+      <c r="D580" t="n">
+        <v>16.3683870967742</v>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>579</v>
+      </c>
+      <c r="B581" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="D581" t="n">
+        <v>451.033129032258</v>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>580</v>
+      </c>
+      <c r="B582" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D582" t="n">
+        <v>2446.129482482625</v>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>581</v>
+      </c>
+      <c r="B583" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>TOUCHSTONE</t>
+        </is>
+      </c>
+      <c r="D583" t="n">
+        <v>33.13036737158834</v>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>582</v>
+      </c>
+      <c r="B584" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>BPTT</t>
+        </is>
+      </c>
+      <c r="D584" t="n">
+        <v>979.2966325</v>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>583</v>
+      </c>
+      <c r="B585" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D585" t="n">
+        <v>462.4207461452858</v>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>584</v>
+      </c>
+      <c r="B586" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>HPCL (Land)</t>
+        </is>
+      </c>
+      <c r="D586" t="n">
+        <v>2</v>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>585</v>
+      </c>
+      <c r="B587" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>HPCL (Offshore)</t>
+        </is>
+      </c>
+      <c r="D587" t="n">
+        <v>16.20455218451762</v>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>586</v>
+      </c>
+      <c r="B588" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>PERENCO</t>
+        </is>
+      </c>
+      <c r="D588" t="n">
+        <v>462.7298139286787</v>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>587</v>
+      </c>
+      <c r="B589" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>PROMAN</t>
+        </is>
+      </c>
+      <c r="D589" t="n">
+        <v>22.03821428571428</v>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>588</v>
+      </c>
+      <c r="B590" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="D590" t="n">
+        <v>493.13425</v>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>589</v>
+      </c>
+      <c r="B591" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D591" t="n">
+        <v>2469.851717789528</v>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>590</v>
+      </c>
+      <c r="B592" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>TOUCHSTONE</t>
+        </is>
+      </c>
+      <c r="D592" t="n">
+        <v>32.02750874533133</v>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="n">
+        <v>591</v>
+      </c>
+      <c r="B593" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>BPTT</t>
+        </is>
+      </c>
+      <c r="D593" t="n">
+        <v>951.4172364516129</v>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>592</v>
+      </c>
+      <c r="B594" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D594" t="n">
+        <v>433.4296774193548</v>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="n">
+        <v>593</v>
+      </c>
+      <c r="B595" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>HPCL (Land)</t>
+        </is>
+      </c>
+      <c r="D595" t="n">
+        <v>2</v>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="n">
+        <v>594</v>
+      </c>
+      <c r="B596" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>HPCL (Offshore)</t>
+        </is>
+      </c>
+      <c r="D596" t="n">
+        <v>14</v>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="n">
+        <v>595</v>
+      </c>
+      <c r="B597" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>PERENCO</t>
+        </is>
+      </c>
+      <c r="D597" t="n">
+        <v>453.9978283873871</v>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="n">
+        <v>596</v>
+      </c>
+      <c r="B598" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>PROMAN</t>
+        </is>
+      </c>
+      <c r="D598" t="n">
+        <v>15.72967741935484</v>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="n">
+        <v>597</v>
+      </c>
+      <c r="B599" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="D599" t="n">
+        <v>468.7631935483871</v>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="n">
+        <v>598</v>
+      </c>
+      <c r="B600" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D600" t="n">
+        <v>2368.188770566943</v>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="n">
+        <v>599</v>
+      </c>
+      <c r="B601" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>TOUCHSTONE</t>
+        </is>
+      </c>
+      <c r="D601" t="n">
+        <v>28.85115734084676</v>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="n">
+        <v>600</v>
+      </c>
+      <c r="B602" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>BPTT</t>
+        </is>
+      </c>
+      <c r="D602" t="n">
+        <v>950.9620363333333</v>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="n">
+        <v>601</v>
+      </c>
+      <c r="B603" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D603" t="n">
+        <v>557.9616666666667</v>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="n">
+        <v>602</v>
+      </c>
+      <c r="B604" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>HPCL (Land)</t>
+        </is>
+      </c>
+      <c r="D604" t="n">
+        <v>2</v>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="n">
+        <v>603</v>
+      </c>
+      <c r="B605" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>HPCL (Offshore)</t>
+        </is>
+      </c>
+      <c r="D605" t="n">
+        <v>14</v>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="n">
+        <v>604</v>
+      </c>
+      <c r="B606" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>PERENCO</t>
+        </is>
+      </c>
+      <c r="D606" t="n">
+        <v>450.0629813334</v>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="n">
+        <v>605</v>
+      </c>
+      <c r="B607" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>PROMAN</t>
+        </is>
+      </c>
+      <c r="D607" t="n">
+        <v>24.957</v>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>606</v>
+      </c>
+      <c r="B608" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="D608" t="n">
+        <v>435.6668</v>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="n">
+        <v>607</v>
+      </c>
+      <c r="B609" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D609" t="n">
+        <v>2466.860874604555</v>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>608</v>
+      </c>
+      <c r="B610" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>TOUCHSTONE</t>
+        </is>
+      </c>
+      <c r="D610" t="n">
+        <v>31.25039027115517</v>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>609</v>
+      </c>
+      <c r="B611" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="C505" t="inlineStr">
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>BPTT</t>
+        </is>
+      </c>
+      <c r="D611" t="n">
+        <v>948.2965261290323</v>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="n">
+        <v>610</v>
+      </c>
+      <c r="B612" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="D612" t="n">
+        <v>553.5893548387098</v>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="n">
+        <v>611</v>
+      </c>
+      <c r="B613" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>HPCL (Land)</t>
+        </is>
+      </c>
+      <c r="D613" t="n">
+        <v>2</v>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="n">
+        <v>612</v>
+      </c>
+      <c r="B614" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>HPCL (Offshore)</t>
+        </is>
+      </c>
+      <c r="D614" t="n">
+        <v>14</v>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="n">
+        <v>613</v>
+      </c>
+      <c r="B615" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>PERENCO</t>
+        </is>
+      </c>
+      <c r="D615" t="n">
+        <v>462.5357477417097</v>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="n">
+        <v>614</v>
+      </c>
+      <c r="B616" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>PROMAN</t>
+        </is>
+      </c>
+      <c r="D616" t="n">
+        <v>21.85129032258065</v>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="n">
+        <v>615</v>
+      </c>
+      <c r="B617" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>SHELL</t>
+        </is>
+      </c>
+      <c r="D617" t="n">
+        <v>407.8799677419355</v>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="n">
+        <v>616</v>
+      </c>
+      <c r="B618" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D618" t="n">
+        <v>2439.380832414558</v>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="n">
+        <v>617</v>
+      </c>
+      <c r="B619" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C619" t="inlineStr">
         <is>
           <t>TOUCHSTONE</t>
         </is>
       </c>
-      <c r="D505" t="n">
+      <c r="D619" t="n">
         <v>29.2279456405902</v>
       </c>
-      <c r="E505" t="inlineStr">
-        <is>
-          <t>Trinidad and Tobago</t>
-        </is>
-      </c>
-      <c r="F505" t="inlineStr">
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
         <is>
           <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
         </is>
@@ -13680,7 +16644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F560"/>
+  <dimension ref="A1:F692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26819,7 +29783,7 @@
         <v>504</v>
       </c>
       <c r="B506" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C506" t="inlineStr">
         <is>
@@ -26827,7 +29791,7 @@
         </is>
       </c>
       <c r="D506" t="n">
-        <v>8.277382967741936</v>
+        <v>18.06</v>
       </c>
       <c r="E506" t="inlineStr">
         <is>
@@ -26836,7 +29800,7 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -26845,7 +29809,7 @@
         <v>505</v>
       </c>
       <c r="B507" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C507" t="inlineStr">
         <is>
@@ -26853,7 +29817,7 @@
         </is>
       </c>
       <c r="D507" t="n">
-        <v>338.8833337741936</v>
+        <v>493.6114341935484</v>
       </c>
       <c r="E507" t="inlineStr">
         <is>
@@ -26862,7 +29826,7 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -26871,7 +29835,7 @@
         <v>506</v>
       </c>
       <c r="B508" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C508" t="inlineStr">
         <is>
@@ -26879,7 +29843,7 @@
         </is>
       </c>
       <c r="D508" t="n">
-        <v>11.99594383870968</v>
+        <v>11.29251183870968</v>
       </c>
       <c r="E508" t="inlineStr">
         <is>
@@ -26888,7 +29852,7 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -26897,7 +29861,7 @@
         <v>507</v>
       </c>
       <c r="B509" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C509" t="inlineStr">
         <is>
@@ -26905,7 +29869,7 @@
         </is>
       </c>
       <c r="D509" t="n">
-        <v>16.34390193548387</v>
+        <v>19.26</v>
       </c>
       <c r="E509" t="inlineStr">
         <is>
@@ -26914,7 +29878,7 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -26923,7 +29887,7 @@
         <v>508</v>
       </c>
       <c r="B510" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C510" t="inlineStr">
         <is>
@@ -26931,7 +29895,7 @@
         </is>
       </c>
       <c r="D510" t="n">
-        <v>48.34645141935484</v>
+        <v>45.26156361290323</v>
       </c>
       <c r="E510" t="inlineStr">
         <is>
@@ -26940,7 +29904,7 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -26949,7 +29913,7 @@
         <v>509</v>
       </c>
       <c r="B511" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
@@ -26957,7 +29921,7 @@
         </is>
       </c>
       <c r="D511" t="n">
-        <v>1241.646029354839</v>
+        <v>1128.5412315858</v>
       </c>
       <c r="E511" t="inlineStr">
         <is>
@@ -26966,7 +29930,7 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -26975,7 +29939,7 @@
         <v>510</v>
       </c>
       <c r="B512" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C512" t="inlineStr">
         <is>
@@ -26983,7 +29947,7 @@
         </is>
       </c>
       <c r="D512" t="n">
-        <v>362.9577847741936</v>
+        <v>492.3735751612903</v>
       </c>
       <c r="E512" t="inlineStr">
         <is>
@@ -26992,7 +29956,7 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27001,7 +29965,7 @@
         <v>511</v>
       </c>
       <c r="B513" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
@@ -27009,7 +29973,7 @@
         </is>
       </c>
       <c r="D513" t="n">
-        <v>0.9179354838709678</v>
+        <v>1.32</v>
       </c>
       <c r="E513" t="inlineStr">
         <is>
@@ -27018,7 +29982,7 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27027,7 +29991,7 @@
         <v>512</v>
       </c>
       <c r="B514" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C514" t="inlineStr">
         <is>
@@ -27035,7 +29999,7 @@
         </is>
       </c>
       <c r="D514" t="n">
-        <v>228.6094279032258</v>
+        <v>236.4</v>
       </c>
       <c r="E514" t="inlineStr">
         <is>
@@ -27044,7 +30008,7 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27053,7 +30017,7 @@
         <v>513</v>
       </c>
       <c r="B515" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C515" t="inlineStr">
         <is>
@@ -27070,7 +30034,7 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27079,7 +30043,7 @@
         <v>514</v>
       </c>
       <c r="B516" s="2" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="C516" t="inlineStr">
         <is>
@@ -27087,7 +30051,7 @@
         </is>
       </c>
       <c r="D516" t="n">
-        <v>2265.978191451613</v>
+        <v>2454.120316392252</v>
       </c>
       <c r="E516" t="inlineStr">
         <is>
@@ -27096,7 +30060,7 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27105,7 +30069,7 @@
         <v>515</v>
       </c>
       <c r="B517" s="2" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="C517" t="inlineStr">
         <is>
@@ -27113,7 +30077,7 @@
         </is>
       </c>
       <c r="D517" t="n">
-        <v>6.407504964285714</v>
+        <v>19.58</v>
       </c>
       <c r="E517" t="inlineStr">
         <is>
@@ -27122,7 +30086,7 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27131,7 +30095,7 @@
         <v>516</v>
       </c>
       <c r="B518" s="2" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="C518" t="inlineStr">
         <is>
@@ -27139,7 +30103,7 @@
         </is>
       </c>
       <c r="D518" t="n">
-        <v>351.51826125</v>
+        <v>474.45</v>
       </c>
       <c r="E518" t="inlineStr">
         <is>
@@ -27148,7 +30112,7 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27157,7 +30121,7 @@
         <v>517</v>
       </c>
       <c r="B519" s="2" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="C519" t="inlineStr">
         <is>
@@ -27165,7 +30129,7 @@
         </is>
       </c>
       <c r="D519" t="n">
-        <v>10.44181525</v>
+        <v>10.43</v>
       </c>
       <c r="E519" t="inlineStr">
         <is>
@@ -27174,7 +30138,7 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27183,7 +30147,7 @@
         <v>518</v>
       </c>
       <c r="B520" s="2" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="C520" t="inlineStr">
         <is>
@@ -27191,7 +30155,7 @@
         </is>
       </c>
       <c r="D520" t="n">
-        <v>17.87620646428572</v>
+        <v>17.51</v>
       </c>
       <c r="E520" t="inlineStr">
         <is>
@@ -27200,7 +30164,7 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27209,7 +30173,7 @@
         <v>519</v>
       </c>
       <c r="B521" s="2" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="C521" t="inlineStr">
         <is>
@@ -27217,7 +30181,7 @@
         </is>
       </c>
       <c r="D521" t="n">
-        <v>48.48315382142857</v>
+        <v>47.98</v>
       </c>
       <c r="E521" t="inlineStr">
         <is>
@@ -27226,7 +30190,7 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27235,7 +30199,7 @@
         <v>520</v>
       </c>
       <c r="B522" s="2" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="C522" t="inlineStr">
         <is>
@@ -27243,7 +30207,7 @@
         </is>
       </c>
       <c r="D522" t="n">
-        <v>1144.444786321429</v>
+        <v>1048.694973965473</v>
       </c>
       <c r="E522" t="inlineStr">
         <is>
@@ -27252,7 +30216,7 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27261,7 +30225,7 @@
         <v>521</v>
       </c>
       <c r="B523" s="2" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="C523" t="inlineStr">
         <is>
@@ -27269,7 +30233,7 @@
         </is>
       </c>
       <c r="D523" t="n">
-        <v>488.8524171071429</v>
+        <v>445.12</v>
       </c>
       <c r="E523" t="inlineStr">
         <is>
@@ -27278,7 +30242,7 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27287,7 +30251,7 @@
         <v>522</v>
       </c>
       <c r="B524" s="2" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="C524" t="inlineStr">
         <is>
@@ -27295,7 +30259,7 @@
         </is>
       </c>
       <c r="D524" t="n">
-        <v>0.6729285714285714</v>
+        <v>1.32</v>
       </c>
       <c r="E524" t="inlineStr">
         <is>
@@ -27304,7 +30268,7 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27313,7 +30277,7 @@
         <v>523</v>
       </c>
       <c r="B525" s="2" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="C525" t="inlineStr">
         <is>
@@ -27321,7 +30285,7 @@
         </is>
       </c>
       <c r="D525" t="n">
-        <v>238.1228512142857</v>
+        <v>244.38</v>
       </c>
       <c r="E525" t="inlineStr">
         <is>
@@ -27330,7 +30294,7 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27339,7 +30303,7 @@
         <v>524</v>
       </c>
       <c r="B526" s="2" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="C526" t="inlineStr">
         <is>
@@ -27347,7 +30311,7 @@
         </is>
       </c>
       <c r="D526" t="n">
-        <v>10.31081414285714</v>
+        <v>10.63</v>
       </c>
       <c r="E526" t="inlineStr">
         <is>
@@ -27356,7 +30320,7 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27365,7 +30329,7 @@
         <v>525</v>
       </c>
       <c r="B527" s="2" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="C527" t="inlineStr">
         <is>
@@ -27373,7 +30337,7 @@
         </is>
       </c>
       <c r="D527" t="n">
-        <v>2317.130739107143</v>
+        <v>2320.094973965473</v>
       </c>
       <c r="E527" t="inlineStr">
         <is>
@@ -27382,7 +30346,7 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27391,7 +30355,7 @@
         <v>526</v>
       </c>
       <c r="B528" s="2" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="C528" t="inlineStr">
         <is>
@@ -27399,7 +30363,7 @@
         </is>
       </c>
       <c r="D528" t="n">
-        <v>6.20377635483871</v>
+        <v>21.64628132258064</v>
       </c>
       <c r="E528" t="inlineStr">
         <is>
@@ -27408,7 +30372,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27417,7 +30381,7 @@
         <v>527</v>
       </c>
       <c r="B529" s="2" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="C529" t="inlineStr">
         <is>
@@ -27425,7 +30389,7 @@
         </is>
       </c>
       <c r="D529" t="n">
-        <v>337.9258685483871</v>
+        <v>437.1602071290323</v>
       </c>
       <c r="E529" t="inlineStr">
         <is>
@@ -27434,7 +30398,7 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27443,7 +30407,7 @@
         <v>528</v>
       </c>
       <c r="B530" s="2" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="C530" t="inlineStr">
         <is>
@@ -27451,7 +30415,7 @@
         </is>
       </c>
       <c r="D530" t="n">
-        <v>10.80526448387097</v>
+        <v>11.96036283870968</v>
       </c>
       <c r="E530" t="inlineStr">
         <is>
@@ -27460,7 +30424,7 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27469,7 +30433,7 @@
         <v>529</v>
       </c>
       <c r="B531" s="2" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="C531" t="inlineStr">
         <is>
@@ -27477,7 +30441,7 @@
         </is>
       </c>
       <c r="D531" t="n">
-        <v>17.22915322580645</v>
+        <v>18.1770685483871</v>
       </c>
       <c r="E531" t="inlineStr">
         <is>
@@ -27486,7 +30450,7 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27495,7 +30459,7 @@
         <v>530</v>
       </c>
       <c r="B532" s="2" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="C532" t="inlineStr">
         <is>
@@ -27503,7 +30467,7 @@
         </is>
       </c>
       <c r="D532" t="n">
-        <v>49.04823716129032</v>
+        <v>45.42</v>
       </c>
       <c r="E532" t="inlineStr">
         <is>
@@ -27512,7 +30476,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27521,7 +30485,7 @@
         <v>531</v>
       </c>
       <c r="B533" s="2" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="C533" t="inlineStr">
         <is>
@@ -27529,7 +30493,7 @@
         </is>
       </c>
       <c r="D533" t="n">
-        <v>1032.746351612903</v>
+        <v>935.8139751990188</v>
       </c>
       <c r="E533" t="inlineStr">
         <is>
@@ -27538,7 +30502,7 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27547,7 +30511,7 @@
         <v>532</v>
       </c>
       <c r="B534" s="2" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="C534" t="inlineStr">
         <is>
@@ -27555,7 +30519,7 @@
         </is>
       </c>
       <c r="D534" t="n">
-        <v>494.8642808709678</v>
+        <v>454.75</v>
       </c>
       <c r="E534" t="inlineStr">
         <is>
@@ -27564,7 +30528,7 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27573,7 +30537,7 @@
         <v>533</v>
       </c>
       <c r="B535" s="2" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="C535" t="inlineStr">
         <is>
@@ -27581,7 +30545,7 @@
         </is>
       </c>
       <c r="D535" t="n">
-        <v>1.052129032258065</v>
+        <v>1.198161290322581</v>
       </c>
       <c r="E535" t="inlineStr">
         <is>
@@ -27590,7 +30554,7 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27599,7 +30563,7 @@
         <v>534</v>
       </c>
       <c r="B536" s="2" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="C536" t="inlineStr">
         <is>
@@ -27607,7 +30571,7 @@
         </is>
       </c>
       <c r="D536" t="n">
-        <v>262.3959126451613</v>
+        <v>259.27</v>
       </c>
       <c r="E536" t="inlineStr">
         <is>
@@ -27616,7 +30580,7 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27625,7 +30589,7 @@
         <v>535</v>
       </c>
       <c r="B537" s="2" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="C537" t="inlineStr">
         <is>
@@ -27633,7 +30597,7 @@
         </is>
       </c>
       <c r="D537" t="n">
-        <v>8.174505483870968</v>
+        <v>8.635613032258064</v>
       </c>
       <c r="E537" t="inlineStr">
         <is>
@@ -27642,7 +30606,7 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27651,7 +30615,7 @@
         <v>536</v>
       </c>
       <c r="B538" s="2" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="C538" t="inlineStr">
         <is>
@@ -27659,7 +30623,7 @@
         </is>
       </c>
       <c r="D538" t="n">
-        <v>2220.445479419355</v>
+        <v>2194.031669360309</v>
       </c>
       <c r="E538" t="inlineStr">
         <is>
@@ -27668,7 +30632,7 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27677,7 +30641,7 @@
         <v>537</v>
       </c>
       <c r="B539" s="2" t="n">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="C539" t="inlineStr">
         <is>
@@ -27685,7 +30649,7 @@
         </is>
       </c>
       <c r="D539" t="n">
-        <v>5.9617682</v>
+        <v>22.28681056666667</v>
       </c>
       <c r="E539" t="inlineStr">
         <is>
@@ -27694,7 +30658,7 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27703,7 +30667,7 @@
         <v>538</v>
       </c>
       <c r="B540" s="2" t="n">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="C540" t="inlineStr">
         <is>
@@ -27711,7 +30675,7 @@
         </is>
       </c>
       <c r="D540" t="n">
-        <v>334.4178742666667</v>
+        <v>440.0235209666667</v>
       </c>
       <c r="E540" t="inlineStr">
         <is>
@@ -27720,7 +30684,7 @@
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27729,7 +30693,7 @@
         <v>539</v>
       </c>
       <c r="B541" s="2" t="n">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="C541" t="inlineStr">
         <is>
@@ -27737,7 +30701,7 @@
         </is>
       </c>
       <c r="D541" t="n">
-        <v>11.84396126666667</v>
+        <v>13.53230716666667</v>
       </c>
       <c r="E541" t="inlineStr">
         <is>
@@ -27746,7 +30710,7 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27755,7 +30719,7 @@
         <v>540</v>
       </c>
       <c r="B542" s="2" t="n">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="C542" t="inlineStr">
         <is>
@@ -27763,7 +30727,7 @@
         </is>
       </c>
       <c r="D542" t="n">
-        <v>17.2291516</v>
+        <v>17.27745313333333</v>
       </c>
       <c r="E542" t="inlineStr">
         <is>
@@ -27772,7 +30736,7 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27781,7 +30745,7 @@
         <v>541</v>
       </c>
       <c r="B543" s="2" t="n">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="C543" t="inlineStr">
         <is>
@@ -27789,7 +30753,7 @@
         </is>
       </c>
       <c r="D543" t="n">
-        <v>49.3296688</v>
+        <v>46.7732533</v>
       </c>
       <c r="E543" t="inlineStr">
         <is>
@@ -27798,7 +30762,7 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27807,7 +30771,7 @@
         <v>542</v>
       </c>
       <c r="B544" s="2" t="n">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="C544" t="inlineStr">
         <is>
@@ -27815,7 +30779,7 @@
         </is>
       </c>
       <c r="D544" t="n">
-        <v>1255.312466666667</v>
+        <v>1038.550198759548</v>
       </c>
       <c r="E544" t="inlineStr">
         <is>
@@ -27824,7 +30788,7 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27833,7 +30797,7 @@
         <v>543</v>
       </c>
       <c r="B545" s="2" t="n">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="C545" t="inlineStr">
         <is>
@@ -27841,7 +30805,7 @@
         </is>
       </c>
       <c r="D545" t="n">
-        <v>360.6807472666667</v>
+        <v>423.4486712333334</v>
       </c>
       <c r="E545" t="inlineStr">
         <is>
@@ -27850,7 +30814,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27859,7 +30823,7 @@
         <v>544</v>
       </c>
       <c r="B546" s="2" t="n">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="C546" t="inlineStr">
         <is>
@@ -27867,7 +30831,7 @@
         </is>
       </c>
       <c r="D546" t="n">
-        <v>1.052129032258065</v>
+        <v>0.8884333333333333</v>
       </c>
       <c r="E546" t="inlineStr">
         <is>
@@ -27876,7 +30840,7 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27885,7 +30849,7 @@
         <v>545</v>
       </c>
       <c r="B547" s="2" t="n">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="C547" t="inlineStr">
         <is>
@@ -27893,7 +30857,7 @@
         </is>
       </c>
       <c r="D547" t="n">
-        <v>261.0417272</v>
+        <v>258.7987916666667</v>
       </c>
       <c r="E547" t="inlineStr">
         <is>
@@ -27902,7 +30866,7 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27911,7 +30875,7 @@
         <v>546</v>
       </c>
       <c r="B548" s="2" t="n">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="C548" t="inlineStr">
         <is>
@@ -27919,7 +30883,7 @@
         </is>
       </c>
       <c r="D548" t="n">
-        <v>10.39455563333333</v>
+        <v>10.47623006666667</v>
       </c>
       <c r="E548" t="inlineStr">
         <is>
@@ -27928,7 +30892,7 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27937,7 +30901,7 @@
         <v>547</v>
       </c>
       <c r="B549" s="2" t="n">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="C549" t="inlineStr">
         <is>
@@ -27945,7 +30909,7 @@
         </is>
       </c>
       <c r="D549" t="n">
-        <v>2307.264049932258</v>
+        <v>2272.055670192882</v>
       </c>
       <c r="E549" t="inlineStr">
         <is>
@@ -27954,7 +30918,7 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27963,7 +30927,7 @@
         <v>548</v>
       </c>
       <c r="B550" s="2" t="n">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="C550" t="inlineStr">
         <is>
@@ -27971,7 +30935,7 @@
         </is>
       </c>
       <c r="D550" t="n">
-        <v>6.805560774193548</v>
+        <v>14.50077790322581</v>
       </c>
       <c r="E550" t="inlineStr">
         <is>
@@ -27980,7 +30944,7 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -27989,7 +30953,7 @@
         <v>549</v>
       </c>
       <c r="B551" s="2" t="n">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="C551" t="inlineStr">
         <is>
@@ -27997,7 +30961,7 @@
         </is>
       </c>
       <c r="D551" t="n">
-        <v>324.0366067419355</v>
+        <v>476.1530795161291</v>
       </c>
       <c r="E551" t="inlineStr">
         <is>
@@ -28006,7 +30970,7 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -28015,7 +30979,7 @@
         <v>550</v>
       </c>
       <c r="B552" s="2" t="n">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="C552" t="inlineStr">
         <is>
@@ -28023,7 +30987,7 @@
         </is>
       </c>
       <c r="D552" t="n">
-        <v>9.712596193548388</v>
+        <v>11.48236903225806</v>
       </c>
       <c r="E552" t="inlineStr">
         <is>
@@ -28032,7 +30996,7 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -28041,7 +31005,7 @@
         <v>551</v>
       </c>
       <c r="B553" s="2" t="n">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="C553" t="inlineStr">
         <is>
@@ -28049,7 +31013,7 @@
         </is>
       </c>
       <c r="D553" t="n">
-        <v>14.89712290322581</v>
+        <v>18.18817967741935</v>
       </c>
       <c r="E553" t="inlineStr">
         <is>
@@ -28058,7 +31022,7 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -28067,7 +31031,7 @@
         <v>552</v>
       </c>
       <c r="B554" s="2" t="n">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="C554" t="inlineStr">
         <is>
@@ -28075,7 +31039,7 @@
         </is>
       </c>
       <c r="D554" t="n">
-        <v>50.86026519354839</v>
+        <v>44.61984693548387</v>
       </c>
       <c r="E554" t="inlineStr">
         <is>
@@ -28084,7 +31048,7 @@
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -28093,7 +31057,7 @@
         <v>553</v>
       </c>
       <c r="B555" s="2" t="n">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="C555" t="inlineStr">
         <is>
@@ -28101,7 +31065,7 @@
         </is>
       </c>
       <c r="D555" t="n">
-        <v>1170.524580967742</v>
+        <v>1209.336635530707</v>
       </c>
       <c r="E555" t="inlineStr">
         <is>
@@ -28110,7 +31074,7 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -28119,7 +31083,7 @@
         <v>554</v>
       </c>
       <c r="B556" s="2" t="n">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="C556" t="inlineStr">
         <is>
@@ -28127,7 +31091,7 @@
         </is>
       </c>
       <c r="D556" t="n">
-        <v>389.3707865806451</v>
+        <v>477.5945863870967</v>
       </c>
       <c r="E556" t="inlineStr">
         <is>
@@ -28136,7 +31100,7 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -28145,7 +31109,7 @@
         <v>555</v>
       </c>
       <c r="B557" s="2" t="n">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="C557" t="inlineStr">
         <is>
@@ -28153,7 +31117,7 @@
         </is>
       </c>
       <c r="D557" t="n">
-        <v>1.026733333333333</v>
+        <v>0.390483870967742</v>
       </c>
       <c r="E557" t="inlineStr">
         <is>
@@ -28162,7 +31126,7 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -28171,7 +31135,7 @@
         <v>556</v>
       </c>
       <c r="B558" s="2" t="n">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="C558" t="inlineStr">
         <is>
@@ -28179,7 +31143,7 @@
         </is>
       </c>
       <c r="D558" t="n">
-        <v>280.9516371290322</v>
+        <v>279.0247813225806</v>
       </c>
       <c r="E558" t="inlineStr">
         <is>
@@ -28188,7 +31152,7 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -28197,7 +31161,7 @@
         <v>557</v>
       </c>
       <c r="B559" s="2" t="n">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="C559" t="inlineStr">
         <is>
@@ -28205,7 +31169,7 @@
         </is>
       </c>
       <c r="D559" t="n">
-        <v>12</v>
+        <v>9.594458870967744</v>
       </c>
       <c r="E559" t="inlineStr">
         <is>
@@ -28214,7 +31178,7 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -28223,22 +31187,3454 @@
         <v>558</v>
       </c>
       <c r="B560" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>2540.885199046836</v>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>559</v>
+      </c>
+      <c r="B561" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Ammonia Derivatives</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>17.72898023333333</v>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>560</v>
+      </c>
+      <c r="B562" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Ammonia Manufacture</t>
+        </is>
+      </c>
+      <c r="D562" t="n">
+        <v>474.7935044</v>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>561</v>
+      </c>
+      <c r="B563" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Cement Manufacture</t>
+        </is>
+      </c>
+      <c r="D563" t="n">
+        <v>14.05000936666667</v>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>562</v>
+      </c>
+      <c r="B564" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Gas Processing</t>
+        </is>
+      </c>
+      <c r="D564" t="n">
+        <v>17.27745313333333</v>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>563</v>
+      </c>
+      <c r="B565" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Iron &amp; Steel Manufacture</t>
+        </is>
+      </c>
+      <c r="D565" t="n">
+        <v>42.966512</v>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>564</v>
+      </c>
+      <c r="B566" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>LNG</t>
+        </is>
+      </c>
+      <c r="D566" t="n">
+        <v>1176.531905564993</v>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>565</v>
+      </c>
+      <c r="B567" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Methanol Manufacture</t>
+        </is>
+      </c>
+      <c r="D567" t="n">
+        <v>418.9097170333333</v>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>566</v>
+      </c>
+      <c r="B568" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>NGC 4" Sales to bpTT</t>
+        </is>
+      </c>
+      <c r="D568" t="n">
+        <v>0.8884333333333333</v>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>567</v>
+      </c>
+      <c r="B569" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Power Generation</t>
+        </is>
+      </c>
+      <c r="D569" t="n">
+        <v>309.1624980666667</v>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>568</v>
+      </c>
+      <c r="B570" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Small Consumers</t>
+        </is>
+      </c>
+      <c r="D570" t="n">
+        <v>10.47623006666667</v>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>569</v>
+      </c>
+      <c r="B571" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D571" t="n">
+        <v>2482.785243198326</v>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>570</v>
+      </c>
+      <c r="B572" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Ammonia Derivatives</t>
+        </is>
+      </c>
+      <c r="D572" t="n">
+        <v>21.5041864516129</v>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>571</v>
+      </c>
+      <c r="B573" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Ammonia Manufacture</t>
+        </is>
+      </c>
+      <c r="D573" t="n">
+        <v>470.2939200967742</v>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>572</v>
+      </c>
+      <c r="B574" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Cement Manufacture</t>
+        </is>
+      </c>
+      <c r="D574" t="n">
+        <v>10.228355</v>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>573</v>
+      </c>
+      <c r="B575" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Gas Processing</t>
+        </is>
+      </c>
+      <c r="D575" t="n">
+        <v>16.9929777419355</v>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>574</v>
+      </c>
+      <c r="B576" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Iron &amp; Steel Manufacture</t>
+        </is>
+      </c>
+      <c r="D576" t="n">
+        <v>43.6415862903226</v>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>575</v>
+      </c>
+      <c r="B577" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>LNG</t>
+        </is>
+      </c>
+      <c r="D577" t="n">
+        <v>1191.271638134725</v>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>576</v>
+      </c>
+      <c r="B578" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Methanol Manufacture</t>
+        </is>
+      </c>
+      <c r="D578" t="n">
+        <v>414.0415447096777</v>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>577</v>
+      </c>
+      <c r="B579" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>NGC 4" Sales to bpTT</t>
+        </is>
+      </c>
+      <c r="D579" t="n">
+        <v>0.651516129032258</v>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>578</v>
+      </c>
+      <c r="B580" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Power Generation</t>
+        </is>
+      </c>
+      <c r="D580" t="n">
+        <v>300.9794670967742</v>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>579</v>
+      </c>
+      <c r="B581" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Small Consumers</t>
+        </is>
+      </c>
+      <c r="D581" t="n">
+        <v>9.70422616129032</v>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>580</v>
+      </c>
+      <c r="B582" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D582" t="n">
+        <v>2479.309417812144</v>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>581</v>
+      </c>
+      <c r="B583" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Ammonia Derivatives</t>
+        </is>
+      </c>
+      <c r="D583" t="n">
+        <v>19.83104158064517</v>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>582</v>
+      </c>
+      <c r="B584" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Ammonia Manufacture</t>
+        </is>
+      </c>
+      <c r="D584" t="n">
+        <v>462.6096174193549</v>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>583</v>
+      </c>
+      <c r="B585" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Cement Manufacture</t>
+        </is>
+      </c>
+      <c r="D585" t="n">
+        <v>13.1944849354839</v>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>584</v>
+      </c>
+      <c r="B586" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Gas Processing</t>
+        </is>
+      </c>
+      <c r="D586" t="n">
+        <v>16.9929777419355</v>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>585</v>
+      </c>
+      <c r="B587" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Iron &amp; Steel Manufacture</t>
+        </is>
+      </c>
+      <c r="D587" t="n">
+        <v>50.0954542580645</v>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>586</v>
+      </c>
+      <c r="B588" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>LNG</t>
+        </is>
+      </c>
+      <c r="D588" t="n">
+        <v>1202.897036820368</v>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>587</v>
+      </c>
+      <c r="B589" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Methanol Manufacture</t>
+        </is>
+      </c>
+      <c r="D589" t="n">
+        <v>405.259396516129</v>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>588</v>
+      </c>
+      <c r="B590" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>NGC 4" Sales to bpTT</t>
+        </is>
+      </c>
+      <c r="D590" t="n">
+        <v>0.651516129032258</v>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>589</v>
+      </c>
+      <c r="B591" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Power Generation</t>
+        </is>
+      </c>
+      <c r="D591" t="n">
+        <v>266.2585112580649</v>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>590</v>
+      </c>
+      <c r="B592" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Small Consumers</t>
+        </is>
+      </c>
+      <c r="D592" t="n">
+        <v>9.70422580645161</v>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="n">
+        <v>591</v>
+      </c>
+      <c r="B593" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D593" t="n">
+        <v>2447.49426246553</v>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>592</v>
+      </c>
+      <c r="B594" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Ammonia Derivatives</t>
+        </is>
+      </c>
+      <c r="D594" t="n">
+        <v>22.09950303333333</v>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="n">
+        <v>593</v>
+      </c>
+      <c r="B595" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Ammonia Manufacture</t>
+        </is>
+      </c>
+      <c r="D595" t="n">
+        <v>478.9648835333333</v>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="n">
+        <v>594</v>
+      </c>
+      <c r="B596" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Cement Manufacture</t>
+        </is>
+      </c>
+      <c r="D596" t="n">
+        <v>10.07672163333333</v>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="n">
+        <v>595</v>
+      </c>
+      <c r="B597" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Gas Processing</t>
+        </is>
+      </c>
+      <c r="D597" t="n">
+        <v>17.32322293333333</v>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="n">
+        <v>596</v>
+      </c>
+      <c r="B598" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Iron &amp; Steel Manufacture</t>
+        </is>
+      </c>
+      <c r="D598" t="n">
+        <v>53.43250846666667</v>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="n">
+        <v>597</v>
+      </c>
+      <c r="B599" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>LNG</t>
+        </is>
+      </c>
+      <c r="D599" t="n">
+        <v>1048.202396278295</v>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="n">
+        <v>598</v>
+      </c>
+      <c r="B600" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Methanol Manufacture</t>
+        </is>
+      </c>
+      <c r="D600" t="n">
+        <v>411.5610615333333</v>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="n">
+        <v>599</v>
+      </c>
+      <c r="B601" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>NGC 4" Sales to bpTT</t>
+        </is>
+      </c>
+      <c r="D601" t="n">
+        <v>0.4539</v>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="n">
+        <v>600</v>
+      </c>
+      <c r="B602" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Power Generation</t>
+        </is>
+      </c>
+      <c r="D602" t="n">
+        <v>268.0412919</v>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="n">
+        <v>601</v>
+      </c>
+      <c r="B603" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Small Consumers</t>
+        </is>
+      </c>
+      <c r="D603" t="n">
+        <v>8.611898533333333</v>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="n">
+        <v>602</v>
+      </c>
+      <c r="B604" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D604" t="n">
+        <v>2318.767387844961</v>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="n">
+        <v>603</v>
+      </c>
+      <c r="B605" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Ammonia Derivatives</t>
+        </is>
+      </c>
+      <c r="D605" t="n">
+        <v>19.14026280645162</v>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="n">
+        <v>604</v>
+      </c>
+      <c r="B606" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Ammonia Manufacture</t>
+        </is>
+      </c>
+      <c r="D606" t="n">
+        <v>444.3798877096774</v>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="n">
+        <v>605</v>
+      </c>
+      <c r="B607" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Cement Manufacture</t>
+        </is>
+      </c>
+      <c r="D607" t="n">
+        <v>9.390899129032258</v>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>606</v>
+      </c>
+      <c r="B608" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Gas Processing</t>
+        </is>
+      </c>
+      <c r="D608" t="n">
+        <v>16.6094529032258</v>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="n">
+        <v>607</v>
+      </c>
+      <c r="B609" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Iron &amp; Steel Manufacture</t>
+        </is>
+      </c>
+      <c r="D609" t="n">
+        <v>32.60713264516129</v>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>608</v>
+      </c>
+      <c r="B610" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>LNG</t>
+        </is>
+      </c>
+      <c r="D610" t="n">
+        <v>1066.62767</v>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>609</v>
+      </c>
+      <c r="B611" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Methanol Manufacture</t>
+        </is>
+      </c>
+      <c r="D611" t="n">
+        <v>404.2072608387097</v>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="n">
+        <v>610</v>
+      </c>
+      <c r="B612" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>NGC 4" Sales to bpTT</t>
+        </is>
+      </c>
+      <c r="D612" t="n">
+        <v>0.5689677419354838</v>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="n">
+        <v>611</v>
+      </c>
+      <c r="B613" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Power Generation</t>
+        </is>
+      </c>
+      <c r="D613" t="n">
+        <v>264.2598774516129</v>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="n">
+        <v>612</v>
+      </c>
+      <c r="B614" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Small Consumers</t>
+        </is>
+      </c>
+      <c r="D614" t="n">
+        <v>11.09258596774194</v>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="n">
+        <v>613</v>
+      </c>
+      <c r="B615" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D615" t="n">
+        <v>2268.883997193548</v>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="n">
+        <v>614</v>
+      </c>
+      <c r="B616" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Ammonia Derivatives</t>
+        </is>
+      </c>
+      <c r="D616" t="n">
+        <v>11.88801756666667</v>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="n">
+        <v>615</v>
+      </c>
+      <c r="B617" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Ammonia Manufacture</t>
+        </is>
+      </c>
+      <c r="D617" t="n">
+        <v>350.6992839</v>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="n">
+        <v>616</v>
+      </c>
+      <c r="B618" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Cement Manufacture</t>
+        </is>
+      </c>
+      <c r="D618" t="n">
+        <v>4.3591246</v>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="n">
+        <v>617</v>
+      </c>
+      <c r="B619" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Gas Processing</t>
+        </is>
+      </c>
+      <c r="D619" t="n">
+        <v>17.42367166666667</v>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="n">
+        <v>618</v>
+      </c>
+      <c r="B620" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Iron &amp; Steel Manufacture</t>
+        </is>
+      </c>
+      <c r="D620" t="n">
+        <v>21.2531626</v>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="n">
+        <v>619</v>
+      </c>
+      <c r="B621" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>LNG</t>
+        </is>
+      </c>
+      <c r="D621" t="n">
+        <v>1110.45371</v>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>620</v>
+      </c>
+      <c r="B622" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Methanol Manufacture</t>
+        </is>
+      </c>
+      <c r="D622" t="n">
+        <v>496.5982670666666</v>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="n">
+        <v>621</v>
+      </c>
+      <c r="B623" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>NGC 4" Sales to bpTT</t>
+        </is>
+      </c>
+      <c r="D623" t="n">
+        <v>0.6294999999999999</v>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="n">
+        <v>622</v>
+      </c>
+      <c r="B624" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Power Generation</t>
+        </is>
+      </c>
+      <c r="D624" t="n">
+        <v>240.5269332666667</v>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="n">
+        <v>623</v>
+      </c>
+      <c r="B625" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Small Consumers</t>
+        </is>
+      </c>
+      <c r="D625" t="n">
+        <v>9.012148333333334</v>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="n">
+        <v>624</v>
+      </c>
+      <c r="B626" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D626" t="n">
+        <v>2262.843819</v>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="n">
+        <v>625</v>
+      </c>
+      <c r="B627" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Ammonia Derivatives</t>
+        </is>
+      </c>
+      <c r="D627" t="n">
+        <v>11.712155</v>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="n">
+        <v>626</v>
+      </c>
+      <c r="B628" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Ammonia Manufacture</t>
+        </is>
+      </c>
+      <c r="D628" t="n">
+        <v>278.8729058387097</v>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="n">
+        <v>627</v>
+      </c>
+      <c r="B629" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Cement Manufacture</t>
+        </is>
+      </c>
+      <c r="D629" t="n">
+        <v>11.87068351612903</v>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="n">
+        <v>628</v>
+      </c>
+      <c r="B630" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Gas Processing</t>
+        </is>
+      </c>
+      <c r="D630" t="n">
+        <v>16.34390222580645</v>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="n">
+        <v>629</v>
+      </c>
+      <c r="B631" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Iron &amp; Steel Manufacture</t>
+        </is>
+      </c>
+      <c r="D631" t="n">
+        <v>48.05481829032259</v>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="n">
+        <v>630</v>
+      </c>
+      <c r="B632" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>LNG</t>
+        </is>
+      </c>
+      <c r="D632" t="n">
+        <v>1238.898254193548</v>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="n">
+        <v>631</v>
+      </c>
+      <c r="B633" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Methanol Manufacture</t>
+        </is>
+      </c>
+      <c r="D633" t="n">
+        <v>440.1060562258065</v>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="n">
+        <v>632</v>
+      </c>
+      <c r="B634" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>NGC 4" Sales to bpTT</t>
+        </is>
+      </c>
+      <c r="D634" t="n">
+        <v>0.6294999999999999</v>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="n">
+        <v>633</v>
+      </c>
+      <c r="B635" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Power Generation</t>
+        </is>
+      </c>
+      <c r="D635" t="n">
+        <v>231.2999066129032</v>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="n">
+        <v>634</v>
+      </c>
+      <c r="B636" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Small Consumers</t>
+        </is>
+      </c>
+      <c r="D636" t="n">
+        <v>7.031944096774193</v>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="n">
+        <v>635</v>
+      </c>
+      <c r="B637" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D637" t="n">
+        <v>2284.820126</v>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/07/MEEI-Consolidated-Monthly-Bulletins_January-December-2025-06-02-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="n">
+        <v>636</v>
+      </c>
+      <c r="B638" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Ammonia Derivatives</t>
+        </is>
+      </c>
+      <c r="D638" t="n">
+        <v>8.277382967741936</v>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="n">
+        <v>637</v>
+      </c>
+      <c r="B639" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Ammonia Manufacture</t>
+        </is>
+      </c>
+      <c r="D639" t="n">
+        <v>338.8833337741936</v>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="n">
+        <v>638</v>
+      </c>
+      <c r="B640" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Cement Manufacture</t>
+        </is>
+      </c>
+      <c r="D640" t="n">
+        <v>11.99594383870968</v>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="n">
+        <v>639</v>
+      </c>
+      <c r="B641" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Gas Processing</t>
+        </is>
+      </c>
+      <c r="D641" t="n">
+        <v>16.34390193548387</v>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="n">
+        <v>640</v>
+      </c>
+      <c r="B642" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Iron &amp; Steel Manufacture</t>
+        </is>
+      </c>
+      <c r="D642" t="n">
+        <v>48.34645141935484</v>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="n">
+        <v>641</v>
+      </c>
+      <c r="B643" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>LNG</t>
+        </is>
+      </c>
+      <c r="D643" t="n">
+        <v>1241.646029354839</v>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="n">
+        <v>642</v>
+      </c>
+      <c r="B644" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Methanol Manufacture</t>
+        </is>
+      </c>
+      <c r="D644" t="n">
+        <v>362.9577847741936</v>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="n">
+        <v>643</v>
+      </c>
+      <c r="B645" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>NGC 4" Sales to bpTT</t>
+        </is>
+      </c>
+      <c r="D645" t="n">
+        <v>0.9179354838709678</v>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="n">
+        <v>644</v>
+      </c>
+      <c r="B646" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Power Generation</t>
+        </is>
+      </c>
+      <c r="D646" t="n">
+        <v>228.6094279032258</v>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="n">
+        <v>645</v>
+      </c>
+      <c r="B647" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Small Consumers</t>
+        </is>
+      </c>
+      <c r="D647" t="n">
+        <v>8</v>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="n">
+        <v>646</v>
+      </c>
+      <c r="B648" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D648" t="n">
+        <v>2265.978191451613</v>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="n">
+        <v>647</v>
+      </c>
+      <c r="B649" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Ammonia Derivatives</t>
+        </is>
+      </c>
+      <c r="D649" t="n">
+        <v>6.407504964285714</v>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="n">
+        <v>648</v>
+      </c>
+      <c r="B650" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Ammonia Manufacture</t>
+        </is>
+      </c>
+      <c r="D650" t="n">
+        <v>351.51826125</v>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="n">
+        <v>649</v>
+      </c>
+      <c r="B651" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Cement Manufacture</t>
+        </is>
+      </c>
+      <c r="D651" t="n">
+        <v>10.44181525</v>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="n">
+        <v>650</v>
+      </c>
+      <c r="B652" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Gas Processing</t>
+        </is>
+      </c>
+      <c r="D652" t="n">
+        <v>17.87620646428572</v>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="n">
+        <v>651</v>
+      </c>
+      <c r="B653" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Iron &amp; Steel Manufacture</t>
+        </is>
+      </c>
+      <c r="D653" t="n">
+        <v>48.48315382142857</v>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="n">
+        <v>652</v>
+      </c>
+      <c r="B654" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>LNG</t>
+        </is>
+      </c>
+      <c r="D654" t="n">
+        <v>1144.444786321429</v>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="n">
+        <v>653</v>
+      </c>
+      <c r="B655" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Methanol Manufacture</t>
+        </is>
+      </c>
+      <c r="D655" t="n">
+        <v>488.8524171071429</v>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="n">
+        <v>654</v>
+      </c>
+      <c r="B656" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>NGC 4" Sales to bpTT</t>
+        </is>
+      </c>
+      <c r="D656" t="n">
+        <v>0.6729285714285714</v>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="n">
+        <v>655</v>
+      </c>
+      <c r="B657" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Power Generation</t>
+        </is>
+      </c>
+      <c r="D657" t="n">
+        <v>238.1228512142857</v>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="n">
+        <v>656</v>
+      </c>
+      <c r="B658" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Small Consumers</t>
+        </is>
+      </c>
+      <c r="D658" t="n">
+        <v>10.31081414285714</v>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="n">
+        <v>657</v>
+      </c>
+      <c r="B659" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D659" t="n">
+        <v>2317.130739107143</v>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="n">
+        <v>658</v>
+      </c>
+      <c r="B660" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Ammonia Derivatives</t>
+        </is>
+      </c>
+      <c r="D660" t="n">
+        <v>6.20377635483871</v>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="n">
+        <v>659</v>
+      </c>
+      <c r="B661" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Ammonia Manufacture</t>
+        </is>
+      </c>
+      <c r="D661" t="n">
+        <v>337.9258685483871</v>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="n">
+        <v>660</v>
+      </c>
+      <c r="B662" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Cement Manufacture</t>
+        </is>
+      </c>
+      <c r="D662" t="n">
+        <v>10.80526448387097</v>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="n">
+        <v>661</v>
+      </c>
+      <c r="B663" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Gas Processing</t>
+        </is>
+      </c>
+      <c r="D663" t="n">
+        <v>17.22915322580645</v>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="n">
+        <v>662</v>
+      </c>
+      <c r="B664" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Iron &amp; Steel Manufacture</t>
+        </is>
+      </c>
+      <c r="D664" t="n">
+        <v>49.04823716129032</v>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="n">
+        <v>663</v>
+      </c>
+      <c r="B665" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>LNG</t>
+        </is>
+      </c>
+      <c r="D665" t="n">
+        <v>1032.746351612903</v>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="n">
+        <v>664</v>
+      </c>
+      <c r="B666" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Methanol Manufacture</t>
+        </is>
+      </c>
+      <c r="D666" t="n">
+        <v>494.8642808709678</v>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="n">
+        <v>665</v>
+      </c>
+      <c r="B667" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>NGC 4" Sales to bpTT</t>
+        </is>
+      </c>
+      <c r="D667" t="n">
+        <v>1.052129032258065</v>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="n">
+        <v>666</v>
+      </c>
+      <c r="B668" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Power Generation</t>
+        </is>
+      </c>
+      <c r="D668" t="n">
+        <v>262.3959126451613</v>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="n">
+        <v>667</v>
+      </c>
+      <c r="B669" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Small Consumers</t>
+        </is>
+      </c>
+      <c r="D669" t="n">
+        <v>8.174505483870968</v>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="n">
+        <v>668</v>
+      </c>
+      <c r="B670" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D670" t="n">
+        <v>2220.445479419355</v>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="n">
+        <v>669</v>
+      </c>
+      <c r="B671" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Ammonia Derivatives</t>
+        </is>
+      </c>
+      <c r="D671" t="n">
+        <v>5.9617682</v>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="n">
+        <v>670</v>
+      </c>
+      <c r="B672" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Ammonia Manufacture</t>
+        </is>
+      </c>
+      <c r="D672" t="n">
+        <v>334.4178742666667</v>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="n">
+        <v>671</v>
+      </c>
+      <c r="B673" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Cement Manufacture</t>
+        </is>
+      </c>
+      <c r="D673" t="n">
+        <v>11.84396126666667</v>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="n">
+        <v>672</v>
+      </c>
+      <c r="B674" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Gas Processing</t>
+        </is>
+      </c>
+      <c r="D674" t="n">
+        <v>17.2291516</v>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="n">
+        <v>673</v>
+      </c>
+      <c r="B675" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Iron &amp; Steel Manufacture</t>
+        </is>
+      </c>
+      <c r="D675" t="n">
+        <v>49.3296688</v>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="n">
+        <v>674</v>
+      </c>
+      <c r="B676" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>LNG</t>
+        </is>
+      </c>
+      <c r="D676" t="n">
+        <v>1255.312466666667</v>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="n">
+        <v>675</v>
+      </c>
+      <c r="B677" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Methanol Manufacture</t>
+        </is>
+      </c>
+      <c r="D677" t="n">
+        <v>360.6807472666667</v>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="n">
+        <v>676</v>
+      </c>
+      <c r="B678" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>NGC 4" Sales to bpTT</t>
+        </is>
+      </c>
+      <c r="D678" t="n">
+        <v>1.052129032258065</v>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="n">
+        <v>677</v>
+      </c>
+      <c r="B679" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Power Generation</t>
+        </is>
+      </c>
+      <c r="D679" t="n">
+        <v>261.0417272</v>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="n">
+        <v>678</v>
+      </c>
+      <c r="B680" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Small Consumers</t>
+        </is>
+      </c>
+      <c r="D680" t="n">
+        <v>10.39455563333333</v>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="n">
+        <v>679</v>
+      </c>
+      <c r="B681" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D681" t="n">
+        <v>2307.264049932258</v>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="n">
+        <v>680</v>
+      </c>
+      <c r="B682" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="C560" t="inlineStr">
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Ammonia Derivatives</t>
+        </is>
+      </c>
+      <c r="D682" t="n">
+        <v>6.805560774193548</v>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="n">
+        <v>681</v>
+      </c>
+      <c r="B683" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Ammonia Manufacture</t>
+        </is>
+      </c>
+      <c r="D683" t="n">
+        <v>324.0366067419355</v>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="n">
+        <v>682</v>
+      </c>
+      <c r="B684" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Cement Manufacture</t>
+        </is>
+      </c>
+      <c r="D684" t="n">
+        <v>9.712596193548388</v>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="n">
+        <v>683</v>
+      </c>
+      <c r="B685" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Gas Processing</t>
+        </is>
+      </c>
+      <c r="D685" t="n">
+        <v>14.89712290322581</v>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="n">
+        <v>684</v>
+      </c>
+      <c r="B686" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Iron &amp; Steel Manufacture</t>
+        </is>
+      </c>
+      <c r="D686" t="n">
+        <v>50.86026519354839</v>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="n">
+        <v>685</v>
+      </c>
+      <c r="B687" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>LNG</t>
+        </is>
+      </c>
+      <c r="D687" t="n">
+        <v>1170.524580967742</v>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="n">
+        <v>686</v>
+      </c>
+      <c r="B688" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Methanol Manufacture</t>
+        </is>
+      </c>
+      <c r="D688" t="n">
+        <v>389.3707865806451</v>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="n">
+        <v>687</v>
+      </c>
+      <c r="B689" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>NGC 4" Sales to bpTT</t>
+        </is>
+      </c>
+      <c r="D689" t="n">
+        <v>1.026733333333333</v>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="n">
+        <v>688</v>
+      </c>
+      <c r="B690" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Power Generation</t>
+        </is>
+      </c>
+      <c r="D690" t="n">
+        <v>280.9516371290322</v>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="n">
+        <v>689</v>
+      </c>
+      <c r="B691" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Small Consumers</t>
+        </is>
+      </c>
+      <c r="D691" t="n">
+        <v>12</v>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="n">
+        <v>690</v>
+      </c>
+      <c r="B692" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C692" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D560" t="n">
+      <c r="D692" t="n">
         <v>2260.185889817204</v>
       </c>
-      <c r="E560" t="inlineStr">
-        <is>
-          <t>Trinidad and Tobago</t>
-        </is>
-      </c>
-      <c r="F560" t="inlineStr">
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
         <is>
           <t>https://www.energy.gov.tt/wp-content/uploads/2026/09/MEEI-Consolidated-Monthly-Bulletins_January-May-2026-16-06-2026.xlsx</t>
         </is>
